--- a/data_src/xlsx表/会员等级表.xlsx
+++ b/data_src/xlsx表/会员等级表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,6 +525,114 @@
         <is>
           <t>本等级对应 type6 条件 id</t>
         </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>零消费路人</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>尚未购买任何专辑，无法参与会员专属线下</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>首专入门</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>已购首张普通专辑，可进会员门槛活动</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>复购常客</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>累计消耗 3 张普通专辑，周边九五折</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中额投入</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>累计消耗 6 张普通专辑，周边九折</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
